--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchCraftDeclarePlan.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importQqchCraftDeclarePlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10278\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\folder\folder-work\hhwy\project\zj\opmp\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFB188B-6271-4382-A017-A19A7AE844E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB9C399-6553-4E2D-B9AD-2E7F73136FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-07-29" sheetId="1" r:id="rId1"/>
@@ -437,12 +437,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,13 +462,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="日期格式错误！" sqref="E1:E1048576" xr:uid="{96F665E3-D045-49F5-A293-BDB9C7B9382E}">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>